--- a/data/systems.xlsx
+++ b/data/systems.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Destinus (via DroneFirms)</t>
+          <t>Destinus (via Naval News)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://media.dronefirms.com/articles/2026/img/destinus-hornet-block1-spanish-navy-frigate.jpg</t>
+          <t>https://www.navalnews.com/naval-news/2026/06/spanish-navy-tests-hornet-block-1-interceptor-from-santa-maria-frigate/</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/</t>
+          <t>https://www.navalnews.com/naval-news/2026/06/spanish-navy-tests-hornet-block-1-interceptor-from-santa-maria-frigate/</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://thedefensepost.com/</t>
+          <t>https://www.thedefensenews.com/news-details/Spanish-Army-Tests-Destinus-Hornet-B1-Counter-Drone-System-in-Container-Launch-Configuration/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Spanish Army Tests Destinus Hornet B1 in Container Launch Config - The Defense Post</t>
+          <t>Spanish Army Tests Destinus Hornet B1 in Container Launch Config - The Defense News</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/</t>
+          <t>https://www.armyrecognition.com/archives/archives-defense-exhibitions/2026-archives-news-defense-exhibitions/eurosatory-2026/knds-containerized-drone-launcher-eurosatory-2026-ukraine-operation-spiderweb</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.euro-sd.com/</t>
+          <t>https://euro-sd.com/2026/06/news/land/51592/knds-showcases-complete-set-of-c-uav-capabilities-at-eurosatory-2026/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>South Korea's Hanwha Systems introduced the Striker-S at Eurosatory 2026, a 35-meter low-observable-hull Medium Uncrewed Surface Vessel (MUSV) with a mission deck for a 10-ton containerized payload module. Hanwha pairs it with a containerized launcher for the Chunmoo missile family, specifically the CTM-ASBM (Chunmoo Tactical Missile - Anti-Ship Ballistic Missile), a GPS/INS- and imaging-infrared-guided 280mm missile that lets the autonomous vessel act as a remote missile carrier extending a task group's strike radius by up to 160 km.</t>
+          <t>South Korea's Hanwha Systems introduced the Striker-S at Eurosatory 2026, a 35-meter low-observable-hull Medium Uncrewed Surface Vessel (MUSV) with a mission deck for a 10-ton containerized payload module. Hanwha pairs it with a containerized launcher for the Chunmoo missile family, specifically the CTM-ASBM (Chunmoo Tactical Missile - Anti-Ship Ballistic Missile), a GPS/INS- and imaging-infrared-guided 280mm missile that lets the autonomous vessel act as a remote missile carrier with Hanwha's Chunmoo missile family spanning roughly 80 km (CGR-080) to 290 km (CTM-290) — the CTM-ASBM shares the ~160 km-range CTM-MR's airframe and propulsion.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.iai.co.il/product/diamond</t>
+          <t>https://www.iai.co.il/product/diamond/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://www.twz.com/</t>
+          <t>https://www.twz.com/news-features/blitzbox-packs-100-weaponized-drones-into-an-unassuming-container</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.slashgear.com/</t>
+          <t>https://www.slashgear.com/2182987/us-military-blitzbox-container-system-deploys-deadly-drones/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1849,6 +1849,16 @@
           <t>Turkey just unveiled a 19.8-ton drone submarine built to launch FPV drone swarms, anti-ship missiles, torpedoes and mines while submerged — Autonocion.com</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2026/05/datum-introduces-strike-capable-sinarit-xluuv/</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Datum Introduces Strike-Capable Sinarit XLUUV - Naval News</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2147,7 +2157,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Iron_beam_01.jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:Or_Eitan_-_Iron_Beam_01.jpg</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2296,7 +2306,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chinese state / commercial shipbuilding (operator undisclosed)</t>
+          <t>Refitted at Hudong-Zhonghua Shipbuilding (CSSC); earlier work at Longhai yard — owner-operator undisclosed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2642,7 +2652,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>In October 2025 the U.S. Navy lashed AeroVironment's Palletized High Energy Laser (P-HEL) — built around the 20-26 kW-class LOCUST laser — to the flight deck of the aircraft carrier USS George H.W. Bush, using Fortem radars and Lockheed's Sanctum battle-management software to track and destroy multiple target drones. The test demonstrated that a palletized/containerized directed-energy weapon can draw on a host ship's organic power to provide functionally unlimited magazine depth against drone swarms without any permanent shipboard integration.</t>
+          <t>In October 2025 the U.S. Navy lashed AeroVironment's Palletized High Energy Laser (P-HEL) — built around the ~20 kW-class LOCUST laser (upgraded to a scalable 20-35 kW+ design announced March 2026) — to the flight deck of the aircraft carrier USS George H.W. Bush, using Fortem radars and Lockheed's Sanctum battle-management software to track and destroy multiple target drones. The test demonstrated that a palletized/containerized directed-energy weapon can draw on a host ship's organic power to provide functionally unlimited magazine depth against drone swarms without any permanent shipboard integration.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2714,7 +2724,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Iranian defence industry (AIO/Shahid Bagheri lineage)</t>
+          <t>Iranian defence industry (developer unspecified in current reporting)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2856,7 +2866,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A truck-carried launcher matching the footprint of a 20-ft ISO container, holding four RBS15 Mk3/Mk4 anti-ship missiles (&gt;300 km) with a shoot-and-scoot relocation under 120 seconds.</t>
+          <t>A truck-carried launcher matching the footprint of a 20-ft ISO container, holding four RBS15 missiles — Mk3 (&gt;200 km), in service now, with the future Mk4 (&gt;300 km) to follow later this decade — with a shoot-and-scoot relocation under 120 seconds.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3070,7 +3080,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A launcher disguised as an ordinary 20/40-ft commercial container, firing up to six Kara Atmaca land-attack/anti-ship cruise missiles (~250-280 km, 220kg warhead), movable by truck, rail or civilian cargo vessel.</t>
+          <t>A launcher disguised as an ordinary 20/40-ft commercial container, firing up to six Kara Atmaca land-attack/anti-ship cruise missiles (Roketsan states &gt;250 km, ~220kg warhead; some outlets report up to 300-400 km), movable by truck and, given standard ISO dimensions, potentially by rail or ship.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3317,6 +3327,16 @@
           <t>Operation Spiderweb — Wikipedia</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>https://www.csis.org/analysis/how-ukraines-spider-web-operation-redefines-asymmetric-warfare</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>How Ukraine's 'Spider Web' Operation Redefines Asymmetric Warfare - CSIS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3478,7 +3498,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A 20/40-ft ISO container concealing a four-cell vertical launcher for ground-launched AARGM-ER anti-radiation missiles (~150 km), aimed at rapidly deployable suppression of enemy radar and air-defense sites.</t>
+          <t>A 20/40-ft ISO container concealing a four-cell vertical launcher for ground-launched AARGM-ER anti-radiation missiles (range undisclosed for this configuration; the air-launched AARGM-ER is rated at over 300 km), aimed at rapidly deployable suppression of enemy radar and air-defense sites.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3545,7 +3565,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Killer Weapons Container</t>
+          <t>Killer Weapons Container (launcher half of the Hunter/Killer CWS pairing)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3585,7 +3605,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Invariant's Containerized Weapon System - APKWS (CWS-A) pairs a 4-pack launcher for APKWS 2.75-inch laser-guided rockets with the L3 Wescam MX-10 RSTA-D sensor suite and radar, claiming better than a 90% kill ratio against Class 2 and 3 UAS threats. The 'Killer Weapons Container' can be reconfigured with Javelin anti-tank missiles or heavy machine guns (M2, M134), managed through an integrated fire-control system and a Threat Illumination Verification System (TIVS).</t>
+          <t>Invariant's Containerized Weapon System (CWS) pairs two containers: a sensor 'Hunter' unit (RPS-42 radar plus an EO/IR turret) and a weapon 'Killer' unit carrying a 4-pack APKWS 2.75-inch laser-guided rocket launcher via the LAND-LGR4, reconfigurable with Javelin anti-tank missiles or heavy machine guns (M2, M134, MK19, M240, M249). Invariant markets the pairing as achieving a high kill ratio against small drones, though independent outlets have not corroborated the manufacturer's specific performance figures.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3595,7 +3615,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Sourced to a single manufacturer product page; independent fielding or test details are not given in the document.</t>
+          <t>Sourced primarily to Invariant's own product page and marketing claims (e.g. a &gt;90% kill-ratio figure and a 'TIVS' name) that are not independently corroborated. Independent reporting (TWZ) describes this as a two-container Hunter/Killer pairing rather than a single all-in-one container.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3615,17 +3635,27 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
+          <t>https://www.twz.com/army-counter-drone-system-pops-out-of-a-shipping-container</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>https://www.invariant-corp.com/cws-a/</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>https://www.invariant-corp.com/cws-a/</t>
-        </is>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>CWS-A — Invariant Corp.</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/army-counter-drone-system-pops-out-of-a-shipping-container</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Army Counter-Drone System Pops Out Of A Shipping Container - The War Zone</t>
         </is>
       </c>
     </row>
@@ -3712,17 +3742,27 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>https://www.twz.com/news-features/new-dutch-navy-support-vessels-will-be-missile-toting-wingmen-to-frigates</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
-        </is>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/news-features/new-dutch-navy-support-vessels-will-be-missile-toting-wingmen-to-frigates</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>New Dutch Navy Support Vessels Will Be Missile-Toting Wingmen To Frigates - TWZ</t>
         </is>
       </c>
     </row>
@@ -3968,17 +4008,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>27 June 2024</t>
+          <t>17 June 2024</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Product reveal reported by TWZ/UAS Vision</t>
+          <t>TWZ product reveal; UAS Vision republished 27 June 2024</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3993,7 +4033,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Rheinmetall and its strategic partner UVision built a modified shipping container holding 126 launch cells for the Hero-120 loitering munition, arranged as three 42-cell arrays for massed swarm-saturation attacks. The Hero-120 itself has a 60 km range, 60-minute endurance, and a gimbaled EO/IR seeker for anti-armor strikes with under 1 meter CEP. Deployable on uncrewed surface vessels, civilian trucks, or static forward operating bases, the MOSA-compliant launcher lets a small force project sea-denial or area-control over a wide zone.</t>
+          <t>Rheinmetall and its strategic partner UVision built a modified shipping container holding 126 launch cells for the Hero-120 loitering munition, arranged as three 42-cell arrays for massed swarm-saturation attacks. The Hero-120 itself has a 60 km range, 60-minute endurance, and a gimbaled EO/IR seeker for anti-armor strikes. Deployable on uncrewed surface vessels, civilian trucks, or static forward operating bases, the launcher lets a small force project sea-denial or area-control over a wide zone.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4075,12 +4115,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>6 August 2024</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4237,7 +4277,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.boeing.com/features/2024/10/boeing-compact-lasers-down-group-3-drones-for-first-time</t>
+          <t>https://www.boeing.com/features/2024/06/boeings-compact-lasers-shine-at-counter-drone-competition</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4503,17 +4543,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>September 2023</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Product marketing/announcement</t>
+          <t>Unveiled at DSEI 2023</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4538,7 +4578,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Described in marketing/analyst literature; fielding status on any specific vessel is not established in the source.</t>
+          <t>First publicly unveiled at DSEI 2023 (Sept 2023). Fielding status on any specific vessel is not established in the sources.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4548,7 +4588,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>IAI (DIAMOND) / Breaking Defense</t>
+          <t>IAI (via Defense Update)</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4558,17 +4598,17 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://breakingdefense.com/2026/05/iais-new-diamond-naval-offering-envisions-flexible-drones-missiles-for-small-vessels/</t>
+          <t>https://defense-update.com/20230912_acdc.html</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
+          <t>https://defense-update.com/20230912_acdc.html</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
+          <t>IAI Unveils All Capabilities Defence Container (ACDC) at DSEI 2023 - Defense Update</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4665,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>North Korea unveiled a fleet of Multiple Launch Rocket Systems disguised as ordinary civilian box trucks and yellow hard-hat dump trucks at a September 2023 military parade, with sliding roofs that open to reveal 12-tube 122mm rocket launchers. In 2026, intelligence reports and open-source video reportedly confirmed these disguised MLRS trucks operating in Russia's Kursk region, demonstrating their utility in heavily surveilled combat zones where distinguishing civilian from military traffic is critical to survival.</t>
+          <t>North Korea unveiled a fleet of Multiple Launch Rocket Systems disguised as ordinary civilian box trucks and yellow hard-hat dump trucks at a September 2023 military parade, with sliding roofs that open to reveal 12-tube 122mm rocket launchers. In January 2025, intelligence reports and open-source video reportedly confirmed these disguised MLRS trucks operating in Russia's Kursk region, demonstrating their utility in heavily surveilled combat zones where distinguishing civilian from military traffic is critical to survival.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4874,7 +4914,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/</t>
+          <t>https://www.armyrecognition.com/uae_defense_news/idex_2023_edge_launches_skyshield_counter-unmanned_aerial_system_c-uas_solution.html</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4884,7 +4924,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.sign4l.ae/</t>
+          <t>https://sign4l.ae/news/edge-unveils-skyshield-counter-uas-solution-idex-2023</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5145,7 +5185,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Product literature/introduction; live-fire demonstrated June 2026</t>
+          <t>Product literature/introduction; live-fire demonstrated April 2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5339,7 +5379,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Beijing Institute of Technology (BIT) Containerized Swarm Launcher Truck</t>
+          <t>China Ordnance Equipment Group (COEG) Containerized Swarm Launcher Truck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5349,7 +5389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Beijing Institute of Technology (BIT), part of a consortium of 70+ Chinese research entities</t>
+          <t>China Ordnance Equipment Group (COEG)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5384,7 +5424,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Chinese state broadcaster CCTV revealed in late 2022 a vehicle-mounted swarm launcher disguised as an ordinary light tactical truck, able to rapidly deploy up to 18 loitering munitions with pop-out wings and V-shaped tails resembling the U.S. Switchblade or Israeli Mini Harpy. It is one module within a broader 'containerized weapon module suite' developed by over 70 Chinese research entities, spanning at least 10 modules covering drones, air defense, anti-ship strike, and electronic warfare. The truck is designed for network-enabled saturation strikes against personnel, light armor, and radar sites.</t>
+          <t>Chinese state broadcaster CCTV revealed in late 2022 a vehicle-mounted swarm launcher, built by China Ordnance Equipment Group, disguised as an ordinary light tactical truck and able to rapidly deploy up to 18 loitering munitions with pop-out wings and V-shaped tails resembling the U.S. Switchblade or Israeli Mini Harpy. The truck is designed for network-enabled saturation strikes against personnel, light armor, and radar sites.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5394,7 +5434,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Details rely on a single state-media reveal; the broader 10-module 'containerized weapon suite' program is only partially disclosed.</t>
+          <t>Builder is China Ordnance Equipment Group (COEG), not the Beijing Institute of Technology. Earlier drafts of this entry conflated it with a separate, later-disclosed (2026) BIT-led EMALS drone-catapult truck program tied to a different vessel (Zhong Da 79) — that is a distinct system, not covered by this entry.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5425,16 +5465,6 @@
       <c r="S47" t="inlineStr">
         <is>
           <t>Drone Swarm Launcher Truck Displayed At China's Big Arms Expo — The War Zone</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>https://asiatimes.com/2026/07/chinas-truck-drone-launcher-hides-airpower-in-civilian-traffic/</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>China's truck drone launcher hides airpower in civilian traffic — Asia Times</t>
         </is>
       </c>
     </row>
@@ -5534,6 +5564,16 @@
           <t>C-DOME: Maritime Application of the Combat-Proven Iron Dome — Rafael</t>
         </is>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2022/11/rafaels-c-dome-completes-final-stage-of-operationalization-aboard-saar-6/</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Rafael's C-DOME Completes Final Stage of Operationalization Aboard Sa'ar 6 - Naval News</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5695,7 +5735,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Electrically powered canister-launched loitering munition (up to 100 km, 10kg warhead); Elbit markets a container launch configuration packing 6 SkyStriker rounds per container for land or naval deployment.</t>
+          <t>Electrically powered canister-launched loitering munition (up to 100 km, 10kg warhead); Elbit markets a canister/container-launch configuration of the SkyStriker, confirmed by a 2023 $95M European contract for the canister variant; exact rounds-per-container and naval-specific deployment details are not publicly disclosed.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5740,12 +5780,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>https://www.battlepolicy.com/skystriker/</t>
+          <t>https://www.elbitsystems.com/news/elbit-systems-awarded-95-million-contract-supply-canister-configuration-skystriker-loitering</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SkyStriker Israel's electric loitering munition - Battle Policy</t>
+          <t>Elbit Systems Awarded $95 Million Contract to Supply Canister Configuration SkyStriker - Elbit Systems</t>
         </is>
       </c>
     </row>
@@ -5845,6 +5885,16 @@
           <t>HUNTER 10 Long-Range Multi Role Loitering Munition — EDGE Group</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>https://www.army-technology.com/projects/skyknight-c-ram-missile-system/</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SkyKnight C-RAM Missile System - Army Technology</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6026,7 +6076,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Naval News</t>
+          <t>Naval News (illustrative Kalibr-K container graphic)</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6419,7 +6469,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Development and swarm-defeat testing at Kirtland AFB</t>
+          <t>AFRL development from 2019; large-scale swarm-defeat demonstration held April 2023 at Kirtland AFB's Chestnut Test Site</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6805,7 +6855,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2018/airshow-china-2018-casic-unveils-new-cm-401-anti-ship-missile</t>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/2018/airshow-china-2018-casic-unveils-new-cm-401-anti-ship-missile</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6917,7 +6967,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>https://equipment.adsinc.com/</t>
+          <t>https://equipment.adsinc.com/liteye-c-auds(containerized-anti-uasdefensesystem)/ecomm-product-detail/402159/</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6927,7 +6977,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>https://www.unmannedairspace.info/</t>
+          <t>https://www.unmannedairspace.info/counter-uas-systems-and-policies/us-air-force-selects-liteye-c-auds-counter-drone-solution-for-critical-infrastructure-protection/</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7188,7 +7238,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Unveiled at IDEX 2017; Saudi operational use vs Houthi drones</t>
+          <t>Unveiled at IDEX 2017; delivered to/operational in Saudi Arabia vs Houthi drones from ~March 2022</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">

--- a/data/systems.xlsx
+++ b/data/systems.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Switzerland (tested by Spain)</t>
+          <t>Switzerland / Spain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.thedefensenews.com/news-details/Spanish-Army-Tests-Destinus-Hornet-B1-Counter-Drone-System-in-Container-Launch-Configuration/</t>
+          <t>https://defence-blog.com/spanish-army-tests-destinus-interceptor-container-launch-system/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Spanish Army Tests Destinus Hornet B1 in Container Launch Config - The Defense News</t>
+          <t>Spanish Army tests Destinus interceptor container launch system - Defence Blog</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Germany / Switzerland-Spain</t>
+          <t>Germany / Switzerland / Spain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>South Korea's Hanwha Systems introduced the Striker-S at Eurosatory 2026, a 35-meter low-observable-hull Medium Uncrewed Surface Vessel (MUSV) with a mission deck for a 10-ton containerized payload module. Hanwha pairs it with a containerized launcher for the Chunmoo missile family, specifically the CTM-ASBM (Chunmoo Tactical Missile - Anti-Ship Ballistic Missile), a GPS/INS- and imaging-infrared-guided 280mm missile that lets the autonomous vessel act as a remote missile carrier with Hanwha's Chunmoo missile family spanning roughly 80 km (CGR-080) to 290 km (CTM-290) — the CTM-ASBM shares the ~160 km-range CTM-MR's airframe and propulsion.</t>
+          <t>South Korea's Hanwha Systems introduced the Striker-S at Eurosatory 2026, a 35-meter low-observable-hull Medium Uncrewed Surface Vessel (MUSV) with a mission deck for a 10-ton containerized payload module. Hanwha pairs it with a containerized launcher for the Chunmoo missile family, specifically the CTM-ASBM (Chunmoo Tactical Missile - Anti-Ship Ballistic Missile), a GPS/INS- and imaging-infrared-guided 280mm missile that lets the autonomous vessel act as a remote missile carrier. The Chunmoo family spans roughly 80 km (CGR-080) to 290 km (CTM-290), with the CTM-ASBM sharing the airframe and propulsion of the ~160 km-range CTM-MR.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Invariant Corporation</t>
+          <t>Invariant Corporation with HDT Global</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4611,6 +4611,16 @@
           <t>IAI Unveils All Capabilities Defence Container (ACDC) at DSEI 2023 - Defense Update</t>
         </is>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4635,7 +4645,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>North Korea (DPRK)</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4914,7 +4924,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/uae_defense_news/idex_2023_edge_launches_skyshield_counter-unmanned_aerial_system_c-uas_solution.html</t>
+          <t>https://armyrecognition.com/news/army-news/2023/idex-2023-edge-launches-skyshield-counter-unmanned-aerial-system-c-uas-solution</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6967,7 +6977,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>https://equipment.adsinc.com/liteye-c-auds(containerized-anti-uasdefensesystem)/ecomm-product-detail/402159/</t>
+          <t>https://equipment.adsinc.com/liteye-c-auds-containerized-anti-uas-defense-system/ecomm-product-detail/402159/</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
